--- a/data/trans_orig/P37A$medicoenfermedad-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicoenfermedad-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21919</t>
+          <t>21602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45954</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>12378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29538</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65676</t>
+          <t>67738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>648058</t>
+          <t>650720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672093</t>
+          <t>672410</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>658813</t>
+          <t>659051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>676014</t>
+          <t>675973</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1316687</t>
+          <t>1314625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343949</t>
+          <t>1343609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>19013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39572</t>
+          <t>41823</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19257</t>
+          <t>18393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40493</t>
+          <t>39956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42648</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74356</t>
+          <t>72979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>922228</t>
+          <t>919977</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>942895</t>
+          <t>942787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>927900</t>
+          <t>928437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>949136</t>
+          <t>950000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1855837</t>
+          <t>1857214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1887545</t>
+          <t>1887727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17134</t>
+          <t>16871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36903</t>
+          <t>36929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31097</t>
+          <t>32307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56891</t>
+          <t>57738</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641606</t>
+          <t>641580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661375</t>
+          <t>661638</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>657429</t>
+          <t>656345</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>672654</t>
+          <t>672639</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1305459</t>
+          <t>1304612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1331253</t>
+          <t>1330043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39808</t>
+          <t>38973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18683</t>
+          <t>18957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40849</t>
+          <t>39846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43332</t>
+          <t>42657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73266</t>
+          <t>71380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>902414</t>
+          <t>903249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922843</t>
+          <t>922933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>997763</t>
+          <t>998766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1019929</t>
+          <t>1019655</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1907568</t>
+          <t>1909454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1937502</t>
+          <t>1938177</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92818</t>
+          <t>93850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134187</t>
+          <t>134078</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76264</t>
+          <t>75676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114793</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180170</t>
+          <t>179404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>236111</t>
+          <t>232890</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3142356</t>
+          <t>3142465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3183725</t>
+          <t>3182693</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3264404</t>
+          <t>3267006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3302933</t>
+          <t>3303521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6419630</t>
+          <t>6422851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6475571</t>
+          <t>6476337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16025</t>
+          <t>16038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36337</t>
+          <t>36634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36020</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36911</t>
+          <t>36849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65614</t>
+          <t>65043</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667132</t>
+          <t>666835</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>687444</t>
+          <t>687431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>661030</t>
+          <t>661298</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>681134</t>
+          <t>680084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1334905</t>
+          <t>1335476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1363608</t>
+          <t>1363670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24294</t>
+          <t>24768</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46993</t>
+          <t>48324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29976</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55990</t>
+          <t>56057</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60394</t>
+          <t>62356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97312</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>970954</t>
+          <t>969623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>993653</t>
+          <t>993179</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>976194</t>
+          <t>976127</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1002208</t>
+          <t>1001298</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1952819</t>
+          <t>1953122</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1989737</t>
+          <t>1987775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17570</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40736</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41820</t>
+          <t>40587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41788</t>
+          <t>40884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75696</t>
+          <t>72948</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>716887</t>
+          <t>717452</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>740053</t>
+          <t>740905</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>735354</t>
+          <t>736587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>758560</t>
+          <t>759506</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1459101</t>
+          <t>1461849</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1493009</t>
+          <t>1493913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26865</t>
+          <t>28020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52399</t>
+          <t>54284</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34365</t>
+          <t>34218</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61282</t>
+          <t>61461</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68664</t>
+          <t>67859</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105774</t>
+          <t>106284</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>895340</t>
+          <t>893455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920874</t>
+          <t>919719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>990619</t>
+          <t>990440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1017536</t>
+          <t>1017683</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1893866</t>
+          <t>1893356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1930976</t>
+          <t>1931781</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104290</t>
+          <t>104014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149818</t>
+          <t>153414</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,77 +4072,77 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>141406</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>116341</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>164928</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>266564</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>234629</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>305274</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>4,37%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>141406</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>119979</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>166399</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>266564</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>236250</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>304336</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3276961</t>
+          <t>3273365</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3322489</t>
+          <t>3322765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,82 +4180,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>95,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3166</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3416903</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3393381</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3441968</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>96,03%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>95,36%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6262</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6718524</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6679814</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6750459</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>95,63%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3416903</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3391910</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3438330</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,03%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6262</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6718524</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6680752</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6748838</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33305</t>
+          <t>35125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19502</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41441</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39974</t>
+          <t>39470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67457</t>
+          <t>68353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>641495</t>
+          <t>639675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>660735</t>
+          <t>660378</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>631398</t>
+          <t>630488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>653337</t>
+          <t>652189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1280182</t>
+          <t>1279286</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1307665</t>
+          <t>1308169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>25327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49979</t>
+          <t>49550</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>17902</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39135</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46807</t>
+          <t>49359</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82676</t>
+          <t>81802</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>972452</t>
+          <t>972881</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>997513</t>
+          <t>997104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1003778</t>
+          <t>1001758</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1026341</t>
+          <t>1025011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1982668</t>
+          <t>1983542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2018537</t>
+          <t>2015985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48211</t>
+          <t>47587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>10334</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27322</t>
+          <t>27487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40518</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68825</t>
+          <t>67486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>711341</t>
+          <t>711965</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>735079</t>
+          <t>735684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>757689</t>
+          <t>757524</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>773589</t>
+          <t>774677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1475738</t>
+          <t>1477077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1504045</t>
+          <t>1506434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>15810</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>35074</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47423</t>
+          <t>45995</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44182</t>
+          <t>44215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76435</t>
+          <t>74873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>902037</t>
+          <t>902493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>921293</t>
+          <t>921757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>996356</t>
+          <t>997784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1022431</t>
+          <t>1021452</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1904911</t>
+          <t>1906473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1937164</t>
+          <t>1937131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97872</t>
+          <t>97222</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140840</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86925</t>
+          <t>86840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129041</t>
+          <t>130473</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>197047</t>
+          <t>198917</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>254881</t>
+          <t>256454</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3253510</t>
+          <t>3254072</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3296478</t>
+          <t>3297128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3415501</t>
+          <t>3414069</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3457617</t>
+          <t>3457702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6684011</t>
+          <t>6682438</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6741845</t>
+          <t>6739975</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>31566</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37591</t>
+          <t>43230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43605</t>
+          <t>47225</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32837</t>
+          <t>38349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53820</t>
+          <t>57980</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70725</t>
+          <t>78792</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56997</t>
+          <t>65603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83939</t>
+          <t>92666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>608321</t>
+          <t>659144</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>597850</t>
+          <t>647480</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>616180</t>
+          <t>667841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>681725</t>
+          <t>686955</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>671510</t>
+          <t>676200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>692493</t>
+          <t>695831</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1290047</t>
+          <t>1346097</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1276833</t>
+          <t>1332223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1303775</t>
+          <t>1359286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53426</t>
+          <t>58276</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23884</t>
+          <t>45472</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74147</t>
+          <t>73668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59349</t>
+          <t>68972</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>56381</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72629</t>
+          <t>85093</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>112774</t>
+          <t>127248</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73455</t>
+          <t>109122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>148024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1139438</t>
+          <t>990641</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1118717</t>
+          <t>975249</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1168980</t>
+          <t>1003445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>899302</t>
+          <t>1002502</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>886022</t>
+          <t>986381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>910688</t>
+          <t>1015093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2038742</t>
+          <t>1993143</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2015165</t>
+          <t>1972367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2078061</t>
+          <t>2011269</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32471</t>
+          <t>36091</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>26394</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45507</t>
+          <t>51336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14831</t>
+          <t>29185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48428</t>
+          <t>49051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>65723</t>
+          <t>74280</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44033</t>
+          <t>60515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83389</t>
+          <t>89189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>672209</t>
+          <t>766982</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>659173</t>
+          <t>751737</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680411</t>
+          <t>776679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>900114</t>
+          <t>774070</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>884938</t>
+          <t>763208</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>918535</t>
+          <t>783074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1572323</t>
+          <t>1541052</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1554657</t>
+          <t>1526143</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1594013</t>
+          <t>1554817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67978</t>
+          <t>71169</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53244</t>
+          <t>57028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85192</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>81904</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56850</t>
+          <t>70096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88861</t>
+          <t>97373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>142552</t>
+          <t>153073</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120434</t>
+          <t>134195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164603</t>
+          <t>174346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>858853</t>
+          <t>918893</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>841639</t>
+          <t>900073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>873587</t>
+          <t>933034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1020358</t>
+          <t>1037137</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1006071</t>
+          <t>1021668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1038082</t>
+          <t>1048945</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1879211</t>
+          <t>1956031</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857160</t>
+          <t>1934758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1901329</t>
+          <t>1974909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>180994</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144690</t>
+          <t>174010</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>213009</t>
+          <t>226084</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>210781</t>
+          <t>236290</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172014</t>
+          <t>213731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>238691</t>
+          <t>260319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>391775</t>
+          <t>433392</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340406</t>
+          <t>402625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>436642</t>
+          <t>471890</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3278823</t>
+          <t>3335660</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3246808</t>
+          <t>3306678</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3315127</t>
+          <t>3358752</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3501499</t>
+          <t>3500664</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3473589</t>
+          <t>3476635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3540266</t>
+          <t>3523223</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6780322</t>
+          <t>6836324</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6735455</t>
+          <t>6797826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6831691</t>
+          <t>6867091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
